--- a/Homepage references.xlsx
+++ b/Homepage references.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mtsportis.sharepoint.com/sites/WorkingspaceIceland/Shared Documents/04.Input to product spec - to development/10.Measurement specification/benchmarks and references/Homepage references/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4baf5f27aaa308f5/Desktop/Measurements Github Repo/measurements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C9B8835-76DE-4971-9A34-FBC49FD6DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{2C9B8835-76DE-4971-9A34-FBC49FD6DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE9CE807-9205-4B2F-AAA0-1F21EFDA4D9A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A392E83A-501C-4FB4-93CE-0DA18CB18A6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A392E83A-501C-4FB4-93CE-0DA18CB18A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -175,6 +175,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,7 +642,7 @@
         <v>8.3659999999999997</v>
       </c>
       <c r="L6" s="1">
-        <v>8.6259999999999994</v>
+        <v>8.1259999999999994</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -725,22 +729,22 @@
         <v>10.574999999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>9.6790000000000003</v>
+        <v>9.9789999999999992</v>
       </c>
       <c r="G9" s="1">
         <v>9.5459999999999994</v>
       </c>
       <c r="H9" s="1">
-        <v>9.1170000000000009</v>
+        <v>9.4969999999999999</v>
       </c>
       <c r="I9" s="1">
         <v>9.4090000000000007</v>
       </c>
       <c r="J9" s="1">
-        <v>9.4890000000000008</v>
+        <v>9.3889999999999993</v>
       </c>
       <c r="K9" s="1">
-        <v>9.5719999999999992</v>
+        <v>9.4719999999999995</v>
       </c>
       <c r="L9" s="1">
         <v>9.3089999999999993</v>
@@ -947,13 +951,13 @@
         <v>8.8260000000000005</v>
       </c>
       <c r="J15" s="1">
-        <v>7.8760000000000003</v>
+        <v>8.31</v>
       </c>
       <c r="K15" s="1">
-        <v>8.6969999999999992</v>
+        <v>8.01</v>
       </c>
       <c r="L15" s="1">
-        <v>8.3989999999999991</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
@@ -1529,10 +1533,10 @@
         <v>10.98</v>
       </c>
       <c r="K12" s="1">
-        <v>9.89</v>
+        <v>9.99</v>
       </c>
       <c r="L12" s="1">
-        <v>9.56</v>
+        <v>9.9600000000000009</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
@@ -2248,10 +2252,10 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="K13" s="1">
-        <v>9.4700000000000006</v>
+        <v>9.23</v>
       </c>
       <c r="L13" s="1">
-        <v>9.6300000000000008</v>
+        <v>9.1300000000000008</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
@@ -2540,6 +2544,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="95ec026b-a4ad-461a-a1d4-c6b927e959dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="951160fc-ff5a-45f7-b050-f4bae28803d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100100A38896A05B94AA42235B986E30978" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4bf31abf3bdff13eb8ffced64c31c2c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="95ec026b-a4ad-461a-a1d4-c6b927e959dc" xmlns:ns3="951160fc-ff5a-45f7-b050-f4bae28803d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5b6ee4a3c3b8aac6ba9922f122fd761" ns2:_="" ns3:_="">
     <xsd:import namespace="95ec026b-a4ad-461a-a1d4-c6b927e959dc"/>
@@ -2746,34 +2770,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="95ec026b-a4ad-461a-a1d4-c6b927e959dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="951160fc-ff5a-45f7-b050-f4bae28803d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED17B6C-AB57-46A8-BFAB-081AE907A653}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD7541A-4617-41A2-8628-D1F9E91F5839}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD7541A-4617-41A2-8628-D1F9E91F5839}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E65F761-03A7-41D7-A089-3F63BCC3640B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="95ec026b-a4ad-461a-a1d4-c6b927e959dc"/>
+    <ds:schemaRef ds:uri="951160fc-ff5a-45f7-b050-f4bae28803d7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E65F761-03A7-41D7-A089-3F63BCC3640B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED17B6C-AB57-46A8-BFAB-081AE907A653}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="95ec026b-a4ad-461a-a1d4-c6b927e959dc"/>
+    <ds:schemaRef ds:uri="951160fc-ff5a-45f7-b050-f4bae28803d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Homepage references.xlsx
+++ b/Homepage references.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4baf5f27aaa308f5/Desktop/Measurements Github Repo/measurements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{2C9B8835-76DE-4971-9A34-FBC49FD6DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE9CE807-9205-4B2F-AAA0-1F21EFDA4D9A}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{2C9B8835-76DE-4971-9A34-FBC49FD6DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5587FD16-0F35-4FC6-B18D-60EE88006A00}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A392E83A-501C-4FB4-93CE-0DA18CB18A6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A392E83A-501C-4FB4-93CE-0DA18CB18A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="25">
   <si>
     <t>9 Years</t>
   </si>
@@ -82,12 +82,6 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>High Performance</t>
-  </si>
-  <si>
     <t>Best</t>
   </si>
   <si>
@@ -113,6 +107,15 @@
   </si>
   <si>
     <t>Average time</t>
+  </si>
+  <si>
+    <t>Needs Improvement (20%)</t>
+  </si>
+  <si>
+    <t>Average (50%)</t>
+  </si>
+  <si>
+    <t>High Performance (80%)</t>
   </si>
 </sst>
 </file>
@@ -498,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10DF481-C2C8-4B08-9383-21801C9971CE}">
-  <dimension ref="B3:L21"/>
+  <dimension ref="B3:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -548,31 +551,31 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1">
-        <v>12.733000000000001</v>
+        <v>14.288511051455121</v>
       </c>
       <c r="F4" s="1">
-        <v>12.033999999999999</v>
+        <v>13.640248103090125</v>
       </c>
       <c r="G4" s="1">
-        <v>11.877000000000001</v>
+        <v>13.293021800659663</v>
       </c>
       <c r="H4" s="1">
-        <v>11.416000000000002</v>
+        <v>12.962366931326143</v>
       </c>
       <c r="I4" s="1">
-        <v>11.103999999999999</v>
+        <v>11.848820149345586</v>
       </c>
       <c r="J4" s="1">
-        <v>10.559000000000001</v>
+        <v>11.193784075902633</v>
       </c>
       <c r="K4" s="1">
-        <v>10.363999999999999</v>
+        <v>11.030203765019976</v>
       </c>
       <c r="L4" s="1">
-        <v>9.9290000000000003</v>
+        <v>10.1214037570925</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -583,31 +586,31 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1">
-        <v>11.346828820452149</v>
+        <v>12.733000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>10.616900433591999</v>
+        <v>12.033999999999999</v>
       </c>
       <c r="G5" s="1">
-        <v>10.611818073825757</v>
+        <v>11.877000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>10.05410946090745</v>
+        <v>11.416000000000002</v>
       </c>
       <c r="I5" s="1">
-        <v>10.405999453608873</v>
+        <v>11.103999999999999</v>
       </c>
       <c r="J5" s="1">
-        <v>9.960213654649186</v>
+        <v>10.559000000000001</v>
       </c>
       <c r="K5" s="1">
-        <v>9.7380337016652962</v>
+        <v>10.363999999999999</v>
       </c>
       <c r="L5" s="1">
-        <v>9.1605515623294025</v>
+        <v>9.9290000000000003</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -618,31 +621,31 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1">
-        <v>9.9610000000000003</v>
+        <v>11.346828820452149</v>
       </c>
       <c r="F6" s="1">
-        <v>9.2330000000000005</v>
+        <v>10.616900433591999</v>
       </c>
       <c r="G6" s="1">
-        <v>9.0050000000000008</v>
+        <v>10.611818073825757</v>
       </c>
       <c r="H6" s="1">
-        <v>8.6820000000000004</v>
+        <v>10.05410946090745</v>
       </c>
       <c r="I6" s="1">
-        <v>8.59</v>
+        <v>10.405999453608873</v>
       </c>
       <c r="J6" s="1">
-        <v>7.9240000000000004</v>
+        <v>9.960213654649186</v>
       </c>
       <c r="K6" s="1">
-        <v>8.3659999999999997</v>
+        <v>9.7380337016652962</v>
       </c>
       <c r="L6" s="1">
-        <v>8.1259999999999994</v>
+        <v>9.1605515623294025</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -650,34 +653,34 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>12.23</v>
+        <v>9.9610000000000003</v>
       </c>
       <c r="F7" s="1">
-        <v>11.73</v>
+        <v>9.2330000000000005</v>
       </c>
       <c r="G7" s="1">
-        <v>11.43</v>
+        <v>9.0050000000000008</v>
       </c>
       <c r="H7" s="1">
-        <v>11.18</v>
+        <v>8.6820000000000004</v>
       </c>
       <c r="I7" s="1">
-        <v>10.99</v>
+        <v>8.59</v>
       </c>
       <c r="J7" s="1">
-        <v>10.76</v>
+        <v>7.9240000000000004</v>
       </c>
       <c r="K7" s="1">
-        <v>10.5</v>
+        <v>8.3659999999999997</v>
       </c>
       <c r="L7" s="1">
-        <v>10.41</v>
+        <v>8.6259999999999994</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -685,34 +688,34 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
-        <v>11.46</v>
+        <v>13.855663022523379</v>
       </c>
       <c r="F8" s="1">
-        <v>11.1</v>
+        <v>13.814015615830352</v>
       </c>
       <c r="G8" s="1">
-        <v>10.81</v>
+        <v>15.220145184709763</v>
       </c>
       <c r="H8" s="1">
-        <v>10.43</v>
+        <v>13.311290400959141</v>
       </c>
       <c r="I8" s="1">
-        <v>10.53</v>
+        <v>13.365237559648266</v>
       </c>
       <c r="J8" s="1">
-        <v>10.029999999999999</v>
+        <v>12.201615450545475</v>
       </c>
       <c r="K8" s="1">
-        <v>9.91</v>
+        <v>11.961182479121476</v>
       </c>
       <c r="L8" s="1">
-        <v>9.86</v>
+        <v>11.157076678125101</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -720,454 +723,664 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1">
-        <v>10.574999999999999</v>
+        <v>12.23</v>
       </c>
       <c r="F9" s="1">
-        <v>9.9789999999999992</v>
+        <v>11.73</v>
       </c>
       <c r="G9" s="1">
-        <v>9.5459999999999994</v>
+        <v>11.43</v>
       </c>
       <c r="H9" s="1">
-        <v>9.4969999999999999</v>
+        <v>11.18</v>
       </c>
       <c r="I9" s="1">
-        <v>9.4090000000000007</v>
+        <v>10.99</v>
       </c>
       <c r="J9" s="1">
-        <v>9.3889999999999993</v>
+        <v>10.76</v>
       </c>
       <c r="K9" s="1">
-        <v>9.4719999999999995</v>
+        <v>10.5</v>
       </c>
       <c r="L9" s="1">
-        <v>9.3089999999999993</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
-        <v>13.85</v>
+        <v>11.46</v>
       </c>
       <c r="F10" s="1">
-        <v>12.19</v>
+        <v>11.1</v>
       </c>
       <c r="G10" s="1">
-        <v>11.7</v>
+        <v>10.81</v>
       </c>
       <c r="H10" s="1">
-        <v>11.23</v>
+        <v>10.43</v>
       </c>
       <c r="I10" s="1">
-        <v>11.25</v>
+        <v>10.53</v>
       </c>
       <c r="J10" s="1">
-        <v>10.86</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>10.74</v>
+        <v>9.91</v>
       </c>
       <c r="L10" s="1">
-        <v>10.25</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1">
-        <v>12.15</v>
+        <v>10.574999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>11</v>
+        <v>9.6790000000000003</v>
       </c>
       <c r="G11" s="1">
-        <v>10.62</v>
+        <v>9.5459999999999994</v>
       </c>
       <c r="H11" s="1">
-        <v>10.29</v>
+        <v>9.1170000000000009</v>
       </c>
       <c r="I11" s="1">
-        <v>10.28</v>
+        <v>9.4090000000000007</v>
       </c>
       <c r="J11" s="1">
-        <v>9.23</v>
+        <v>9.4890000000000008</v>
       </c>
       <c r="K11" s="1">
-        <v>9.4499999999999993</v>
+        <v>9.5719999999999992</v>
       </c>
       <c r="L11" s="1">
-        <v>9.59</v>
+        <v>9.3089999999999993</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E12" s="1">
-        <v>9.9610000000000003</v>
+        <v>15.987988637889131</v>
       </c>
       <c r="F12" s="1">
-        <v>9.2330000000000005</v>
+        <v>15.572273889201824</v>
       </c>
       <c r="G12" s="1">
-        <v>9.0050000000000008</v>
+        <v>15.053213058258347</v>
       </c>
       <c r="H12" s="1">
-        <v>8.6820000000000004</v>
+        <v>14.167160554524832</v>
       </c>
       <c r="I12" s="1">
-        <v>8.59</v>
+        <v>13.794269561069219</v>
       </c>
       <c r="J12" s="1">
-        <v>7.9240000000000004</v>
+        <v>12.956670454600873</v>
       </c>
       <c r="K12" s="1">
-        <v>8.3659999999999997</v>
+        <v>13.178037918315043</v>
       </c>
       <c r="L12" s="1">
-        <v>8.2100000000000009</v>
+        <v>13.39984020262929</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1">
-        <v>14.46</v>
+        <v>13.844999999999999</v>
       </c>
       <c r="F13" s="1">
-        <v>13.37</v>
+        <v>12.446000000000002</v>
       </c>
       <c r="G13" s="1">
-        <v>13.18</v>
+        <v>11.808000000000002</v>
       </c>
       <c r="H13" s="1">
-        <v>11.85</v>
+        <v>11.154999999999998</v>
       </c>
       <c r="I13" s="1">
-        <v>11.53</v>
+        <v>11.577599999999999</v>
       </c>
       <c r="J13" s="1">
-        <v>11.25</v>
+        <v>10.880999999999998</v>
       </c>
       <c r="K13" s="1">
-        <v>10.72</v>
+        <v>10.98</v>
       </c>
       <c r="L13" s="1">
-        <v>10.74</v>
+        <v>10.521000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1">
-        <v>13.2</v>
+        <v>12.156000632838809</v>
       </c>
       <c r="F14" s="1">
-        <v>12.03</v>
+        <v>11.030749344776938</v>
       </c>
       <c r="G14" s="1">
-        <v>11.23</v>
+        <v>10.70361851495923</v>
       </c>
       <c r="H14" s="1">
-        <v>10.53</v>
+        <v>10.081766169748226</v>
       </c>
       <c r="I14" s="1">
-        <v>10.73</v>
+        <v>10.248544047521285</v>
       </c>
       <c r="J14" s="1">
-        <v>9.7799999999999994</v>
+        <v>9.6455123974865149</v>
       </c>
       <c r="K14" s="1">
-        <v>9.61</v>
+        <v>9.3518868866449232</v>
       </c>
       <c r="L14" s="1">
-        <v>9.6300000000000008</v>
+        <v>9.1785042314062117</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>11.728999999999999</v>
+        <v>9.1726588639336732</v>
       </c>
       <c r="F15" s="1">
-        <v>9.6530000000000005</v>
+        <v>8.6741353772454346</v>
       </c>
       <c r="G15" s="1">
-        <v>9.24</v>
+        <v>8.0932399573808258</v>
       </c>
       <c r="H15" s="1">
-        <v>9.0649999999999995</v>
+        <v>7.7533737771005748</v>
       </c>
       <c r="I15" s="1">
-        <v>8.8260000000000005</v>
+        <v>7.4603356797274323</v>
       </c>
       <c r="J15" s="1">
-        <v>8.31</v>
+        <v>7.8347794911925126</v>
       </c>
       <c r="K15" s="1">
-        <v>8.01</v>
+        <v>7.7356437679369687</v>
       </c>
       <c r="L15" s="1">
-        <v>8.15</v>
+        <v>7.1886060932665981</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1">
-        <v>5.46</v>
+        <v>19.034958717039011</v>
       </c>
       <c r="F16" s="1">
-        <v>5.49</v>
+        <v>19.505469029835218</v>
       </c>
       <c r="G16" s="1">
-        <v>5.23</v>
+        <v>19.204576902341461</v>
       </c>
       <c r="H16" s="1">
-        <v>5.1100000000000003</v>
+        <v>16.664008856445896</v>
       </c>
       <c r="I16" s="1">
-        <v>4.96</v>
+        <v>14.611626715152706</v>
       </c>
       <c r="J16" s="1">
-        <v>4.7300000000000004</v>
+        <v>13.919917037069357</v>
       </c>
       <c r="K16" s="1">
-        <v>4.59</v>
+        <v>14.182070197143291</v>
       </c>
       <c r="L16" s="1">
-        <v>4.4800000000000004</v>
+        <v>13.193090899476502</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1">
-        <v>5.22</v>
+        <v>14.763</v>
       </c>
       <c r="F17" s="1">
-        <v>5.2</v>
+        <v>13.941850000000002</v>
       </c>
       <c r="G17" s="1">
-        <v>5</v>
+        <v>13.199399999999997</v>
       </c>
       <c r="H17" s="1">
-        <v>4.8600000000000003</v>
+        <v>12.361500000000003</v>
       </c>
       <c r="I17" s="1">
-        <v>4.66</v>
+        <v>11.925000000000001</v>
       </c>
       <c r="J17" s="1">
-        <v>4.4000000000000004</v>
+        <v>11.596700000000002</v>
       </c>
       <c r="K17" s="1">
-        <v>4.3</v>
+        <v>11.457600000000001</v>
       </c>
       <c r="L17" s="1">
-        <v>4.24</v>
+        <v>11.070000000000002</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E18" s="1">
-        <v>5.0890000000000004</v>
+        <v>13.32107853604232</v>
       </c>
       <c r="F18" s="1">
-        <v>4.7969999999999997</v>
+        <v>12.58068824823707</v>
       </c>
       <c r="G18" s="1">
-        <v>4.46</v>
+        <v>11.200015344976205</v>
       </c>
       <c r="H18" s="1">
-        <v>4.077</v>
+        <v>11.320818815277287</v>
       </c>
       <c r="I18" s="1">
-        <v>4.1210000000000004</v>
+        <v>10.813734369229584</v>
       </c>
       <c r="J18" s="1">
-        <v>3.9119999999999999</v>
+        <v>10.97727878643812</v>
       </c>
       <c r="K18" s="1">
-        <v>4.0279999999999996</v>
+        <v>10.757834214551558</v>
       </c>
       <c r="L18" s="1">
-        <v>3.86</v>
+        <v>10.836660725628219</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="1">
-        <v>5.92</v>
+        <v>9.7571181806778338</v>
       </c>
       <c r="F19" s="1">
-        <v>5.33</v>
+        <v>9.3995344066912594</v>
       </c>
       <c r="G19" s="1">
-        <v>5.19</v>
+        <v>8.3528146402669368</v>
       </c>
       <c r="H19" s="1">
-        <v>5.14</v>
+        <v>8.8546341040833862</v>
       </c>
       <c r="I19" s="1">
-        <v>5.17</v>
+        <v>8.3119229221075717</v>
       </c>
       <c r="J19" s="1">
-        <v>4.8499999999999996</v>
+        <v>8.5181491034586436</v>
       </c>
       <c r="K19" s="1">
-        <v>4.87</v>
+        <v>8.0666364430534525</v>
       </c>
       <c r="L19" s="1">
-        <v>4.76</v>
+        <v>8.3305615100636157</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1">
-        <v>5.59</v>
+        <v>6.2146121063440534</v>
       </c>
       <c r="F20" s="1">
-        <v>5.04</v>
+        <v>6.1087271312044846</v>
       </c>
       <c r="G20" s="1">
-        <v>4.96</v>
+        <v>6.0214043175131424</v>
       </c>
       <c r="H20" s="1">
-        <v>4.88</v>
+        <v>5.5642433609399262</v>
       </c>
       <c r="I20" s="1">
-        <v>4.79</v>
+        <v>5.4859663459259833</v>
       </c>
       <c r="J20" s="1">
-        <v>4.66</v>
+        <v>5.4732743510317396</v>
       </c>
       <c r="K20" s="1">
-        <v>4.6399999999999997</v>
+        <v>5.3287507305270987</v>
       </c>
       <c r="L20" s="1">
-        <v>4.53</v>
+        <v>4.8793795156285258</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5.8692105259999998</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5.7692105260000002</v>
+      </c>
+      <c r="G21" s="1">
+        <v>5.6498478260000002</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5.2883128830000006</v>
+      </c>
+      <c r="I21" s="1">
+        <v>5.1603242189999987</v>
+      </c>
+      <c r="J21" s="1">
+        <v>5.1494507040000004</v>
+      </c>
+      <c r="K21" s="1">
+        <v>4.8918211920000001</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4.5671078429999996</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5.282</v>
-      </c>
-      <c r="F21" s="1">
-        <v>4.5460000000000003</v>
-      </c>
-      <c r="G21" s="1">
-        <v>4.6859999999999999</v>
-      </c>
-      <c r="H21" s="1">
-        <v>4.343</v>
-      </c>
-      <c r="I21" s="1">
-        <v>4.375</v>
-      </c>
-      <c r="J21" s="1">
-        <v>4.3159999999999998</v>
-      </c>
-      <c r="K21" s="1">
-        <v>4.1970000000000001</v>
-      </c>
-      <c r="L21" s="1">
-        <v>4.0629999999999997</v>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5.5430060008643292</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5.4485638952981823</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5.3012185818706659</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5.0260657800883184</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4.8540119217051485</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4.84478592744534</v>
+      </c>
+      <c r="K22" s="1">
+        <v>4.4907175780266329</v>
+      </c>
+      <c r="L22" s="1">
+        <v>4.2748210059871257</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="1">
+        <v>5.0111156271179498</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4.9257359051788709</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4.7378153333043356</v>
+      </c>
+      <c r="H23" s="1">
+        <v>4.5947344371909686</v>
+      </c>
+      <c r="I23" s="1">
+        <v>4.3572967450933611</v>
+      </c>
+      <c r="J23" s="1">
+        <v>4.3506022021859723</v>
+      </c>
+      <c r="K23" s="1">
+        <v>3.8616233058373628</v>
+      </c>
+      <c r="L23" s="1">
+        <v>3.8040510185046021</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6.42638205662319</v>
+      </c>
+      <c r="F24" s="1">
+        <v>6.2624078262350755</v>
+      </c>
+      <c r="G24" s="1">
+        <v>6.3710152017122237</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5.8477603318965272</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5.5375560621601672</v>
+      </c>
+      <c r="J24" s="1">
+        <v>5.3502959942121686</v>
+      </c>
+      <c r="K24" s="1">
+        <v>5.1539004645202322</v>
+      </c>
+      <c r="L24" s="1">
+        <v>5.0842789242443844</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6.0692105259999991</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5.9692105259999995</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5.9544999999999995</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5.4704712640000013</v>
+      </c>
+      <c r="I25" s="1">
+        <v>5.3041999999999998</v>
+      </c>
+      <c r="J25" s="1">
+        <v>5.1058217819999996</v>
+      </c>
+      <c r="K25" s="1">
+        <v>4.9637402599999998</v>
+      </c>
+      <c r="L25" s="1">
+        <v>4.8677068969999997</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="1">
+        <v>5.7318902119966229</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5.6897403191210936</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5.5652151387852768</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5.1175243429554582</v>
+      </c>
+      <c r="I26" s="1">
+        <v>5.0806777076718008</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4.8725184733231517</v>
+      </c>
+      <c r="K26" s="1">
+        <v>4.7805962762298781</v>
+      </c>
+      <c r="L26" s="1">
+        <v>4.6603600605218176</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>5.1818750709961074</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5.2282394833360701</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4.9394807517476087</v>
+      </c>
+      <c r="H27" s="1">
+        <v>4.5494855799787999</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4.7090745949816961</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4.4866301607370627</v>
+      </c>
+      <c r="K27" s="1">
+        <v>4.4738272069408875</v>
+      </c>
+      <c r="L27" s="1">
+        <v>4.3158738740084193</v>
       </c>
     </row>
   </sheetData>
@@ -1186,7 +1399,7 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -1197,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -1232,31 +1445,31 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1">
-        <v>12.28</v>
+        <v>12.894</v>
       </c>
       <c r="F4" s="1">
-        <v>12.34</v>
+        <v>12.7102</v>
       </c>
       <c r="G4" s="1">
-        <v>11.65</v>
+        <v>11.999500000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>10.99</v>
+        <v>11.5395</v>
       </c>
       <c r="I4" s="1">
-        <v>10.83</v>
+        <v>11.0466</v>
       </c>
       <c r="J4" s="1">
-        <v>10.79</v>
+        <v>10.250499999999999</v>
       </c>
       <c r="K4" s="1">
         <v>10.36</v>
       </c>
       <c r="L4" s="1">
-        <v>10.28</v>
+        <v>10.074399999999999</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -1267,31 +1480,31 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1">
-        <v>12.3</v>
+        <v>12.915000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>11.74</v>
+        <v>12.0922</v>
       </c>
       <c r="G5" s="1">
-        <v>11.56</v>
+        <v>11.9068</v>
       </c>
       <c r="H5" s="1">
-        <v>11.23</v>
+        <v>11.791500000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>10.96</v>
+        <v>11.179200000000002</v>
       </c>
       <c r="J5" s="1">
-        <v>10.81</v>
+        <v>10.269500000000001</v>
       </c>
       <c r="K5" s="1">
         <v>10.42</v>
       </c>
       <c r="L5" s="1">
-        <v>10.119999999999999</v>
+        <v>9.9175999999999984</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -1302,31 +1515,31 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1">
-        <v>11.89</v>
+        <v>12.484500000000001</v>
       </c>
       <c r="F6" s="1">
-        <v>11.75</v>
+        <v>12.102500000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>11.32</v>
+        <v>11.659600000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>11.09</v>
+        <v>11.644500000000001</v>
       </c>
       <c r="I6" s="1">
-        <v>10.56</v>
+        <v>10.7712</v>
       </c>
       <c r="J6" s="1">
-        <v>10.37</v>
+        <v>9.8514999999999979</v>
       </c>
       <c r="K6" s="1">
         <v>10.11</v>
       </c>
       <c r="L6" s="1">
-        <v>9.51</v>
+        <v>9.319799999999999</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -1334,34 +1547,34 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
-        <v>12.26</v>
+        <v>13.486000000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>12.31</v>
+        <v>14.156499999999999</v>
       </c>
       <c r="G7" s="1">
-        <v>11.61</v>
+        <v>13.931999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>11.02</v>
+        <v>13.223999999999998</v>
       </c>
       <c r="I7" s="1">
-        <v>10.87</v>
+        <v>13.043999999999999</v>
       </c>
       <c r="J7" s="1">
-        <v>10.76</v>
+        <v>12.373999999999999</v>
       </c>
       <c r="K7" s="1">
-        <v>10.31</v>
+        <v>11.8565</v>
       </c>
       <c r="L7" s="1">
-        <v>10.25</v>
+        <v>11.275</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -1369,34 +1582,34 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
-        <v>12.73</v>
+        <v>14.003000000000002</v>
       </c>
       <c r="F8" s="1">
-        <v>11.85</v>
+        <v>13.627499999999998</v>
       </c>
       <c r="G8" s="1">
-        <v>11.44</v>
+        <v>13.728</v>
       </c>
       <c r="H8" s="1">
-        <v>11.56</v>
+        <v>13.872</v>
       </c>
       <c r="I8" s="1">
-        <v>11.39</v>
+        <v>13.668000000000001</v>
       </c>
       <c r="J8" s="1">
-        <v>11.09</v>
+        <v>12.753499999999999</v>
       </c>
       <c r="K8" s="1">
-        <v>10.72</v>
+        <v>12.327999999999999</v>
       </c>
       <c r="L8" s="1">
-        <v>10.65</v>
+        <v>11.715000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -1404,454 +1617,454 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
-        <v>11.98</v>
+        <v>13.178000000000001</v>
       </c>
       <c r="F9" s="1">
-        <v>11.51</v>
+        <v>13.236499999999999</v>
       </c>
       <c r="G9" s="1">
-        <v>10.96</v>
+        <v>13.152000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>10.89</v>
+        <v>13.068</v>
       </c>
       <c r="I9" s="1">
-        <v>10.68</v>
+        <v>12.815999999999999</v>
       </c>
       <c r="J9" s="1">
-        <v>10.19</v>
+        <v>11.718499999999999</v>
       </c>
       <c r="K9" s="1">
-        <v>10.08</v>
+        <v>11.591999999999999</v>
       </c>
       <c r="L9" s="1">
-        <v>10.130000000000001</v>
+        <v>11.143000000000002</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
-        <v>13.56</v>
+        <v>14.238000000000001</v>
       </c>
       <c r="F10" s="1">
-        <v>12.41</v>
+        <v>13.0305</v>
       </c>
       <c r="G10" s="1">
-        <v>11.46</v>
+        <v>12.033000000000001</v>
       </c>
       <c r="H10" s="1">
         <v>11.09</v>
       </c>
       <c r="I10" s="1">
-        <v>10.58</v>
+        <v>11.109</v>
       </c>
       <c r="J10" s="1">
-        <v>9.15</v>
+        <v>9.6074999999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>9.2100000000000009</v>
+        <v>9.6705000000000005</v>
       </c>
       <c r="L10" s="1">
-        <v>9.3000000000000007</v>
+        <v>9.7650000000000006</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1">
-        <v>13.5</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>12.38</v>
+        <v>12.999000000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>12.09</v>
+        <v>12.6945</v>
       </c>
       <c r="H11" s="1">
         <v>12.06</v>
       </c>
       <c r="I11" s="1">
-        <v>11.63</v>
+        <v>12.211500000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>11.15</v>
+        <v>11.707500000000001</v>
       </c>
       <c r="K11" s="1">
-        <v>11.26</v>
+        <v>11.823</v>
       </c>
       <c r="L11" s="1">
-        <v>11.01</v>
+        <v>11.560500000000001</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1">
-        <v>12.02</v>
+        <v>12.621</v>
       </c>
       <c r="F12" s="1">
-        <v>11.98</v>
+        <v>12.579000000000001</v>
       </c>
       <c r="G12" s="1">
-        <v>11.28</v>
+        <v>11.843999999999999</v>
       </c>
       <c r="H12" s="1">
         <v>11.19</v>
       </c>
       <c r="I12" s="1">
-        <v>11.45</v>
+        <v>12.022499999999999</v>
       </c>
       <c r="J12" s="1">
-        <v>10.98</v>
+        <v>11.529000000000002</v>
       </c>
       <c r="K12" s="1">
-        <v>9.99</v>
+        <v>10.384500000000001</v>
       </c>
       <c r="L12" s="1">
-        <v>9.9600000000000009</v>
+        <v>10.038</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1">
-        <v>14.34</v>
+        <v>15.057</v>
       </c>
       <c r="F13" s="1">
-        <v>13.23</v>
+        <v>13.891500000000001</v>
       </c>
       <c r="G13" s="1">
-        <v>13.22</v>
+        <v>13.881000000000002</v>
       </c>
       <c r="H13" s="1">
         <v>11.13</v>
       </c>
       <c r="I13" s="1">
-        <v>11.13</v>
+        <v>11.686500000000001</v>
       </c>
       <c r="J13" s="1">
-        <v>10.42</v>
+        <v>10.941000000000001</v>
       </c>
       <c r="K13" s="1">
-        <v>9.4700000000000006</v>
+        <v>9.9435000000000002</v>
       </c>
       <c r="L13" s="1">
-        <v>9.6300000000000008</v>
+        <v>10.111500000000001</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1">
-        <v>15.2</v>
+        <v>15.959999999999999</v>
       </c>
       <c r="F14" s="1">
-        <v>14.2</v>
+        <v>14.91</v>
       </c>
       <c r="G14" s="1">
-        <v>12.3</v>
+        <v>12.915000000000001</v>
       </c>
       <c r="H14" s="1">
         <v>12.63</v>
       </c>
       <c r="I14" s="1">
-        <v>12.18</v>
+        <v>12.789</v>
       </c>
       <c r="J14" s="1">
-        <v>11.83</v>
+        <v>12.4215</v>
       </c>
       <c r="K14" s="1">
-        <v>11.53</v>
+        <v>12.1065</v>
       </c>
       <c r="L14" s="1">
-        <v>11.97</v>
+        <v>12.568500000000002</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1">
-        <v>14.1</v>
+        <v>14.805</v>
       </c>
       <c r="F15" s="1">
-        <v>13</v>
+        <v>13.65</v>
       </c>
       <c r="G15" s="1">
-        <v>12.5</v>
+        <v>13.125</v>
       </c>
       <c r="H15" s="1">
         <v>12.3</v>
       </c>
       <c r="I15" s="1">
-        <v>11.6</v>
+        <v>12.18</v>
       </c>
       <c r="J15" s="1">
-        <v>10.78</v>
+        <v>11.318999999999999</v>
       </c>
       <c r="K15" s="1">
-        <v>9.85</v>
+        <v>10.342499999999999</v>
       </c>
       <c r="L15" s="1">
-        <v>9.06</v>
+        <v>9.5130000000000017</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1">
-        <v>5.6</v>
+        <v>5.88</v>
       </c>
       <c r="F16" s="1">
-        <v>5.53</v>
+        <v>5.8065000000000007</v>
       </c>
       <c r="G16" s="1">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="H16" s="1">
         <v>5.07</v>
       </c>
       <c r="I16" s="1">
-        <v>4.8600000000000003</v>
+        <v>5.1030000000000006</v>
       </c>
       <c r="J16" s="1">
-        <v>4.72</v>
+        <v>4.9559999999999995</v>
       </c>
       <c r="K16" s="1">
-        <v>4.53</v>
+        <v>4.7565000000000008</v>
       </c>
       <c r="L16" s="1">
-        <v>4.43</v>
+        <v>4.6514999999999995</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1">
-        <v>5.4</v>
+        <v>5.6700000000000008</v>
       </c>
       <c r="F17" s="1">
-        <v>5.16</v>
+        <v>5.4180000000000001</v>
       </c>
       <c r="G17" s="1">
-        <v>5.0599999999999996</v>
+        <v>5.4648000000000003</v>
       </c>
       <c r="H17" s="1">
         <v>5.36</v>
       </c>
       <c r="I17" s="1">
-        <v>5.22</v>
+        <v>5.4809999999999999</v>
       </c>
       <c r="J17" s="1">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="K17" s="1">
-        <v>4.75</v>
+        <v>4.9874999999999998</v>
       </c>
       <c r="L17" s="1">
-        <v>4.5999999999999996</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1">
-        <v>5.61</v>
+        <v>5.8905000000000003</v>
       </c>
       <c r="F18" s="1">
-        <v>5.21</v>
+        <v>5.4705000000000004</v>
       </c>
       <c r="G18" s="1">
-        <v>5.23</v>
+        <v>5.6484000000000005</v>
       </c>
       <c r="H18" s="1">
         <v>5.0999999999999996</v>
       </c>
       <c r="I18" s="1">
-        <v>5.13</v>
+        <v>5.3864999999999998</v>
       </c>
       <c r="J18" s="1">
-        <v>5.01</v>
+        <v>5.2605000000000004</v>
       </c>
       <c r="K18" s="1">
-        <v>4.63</v>
+        <v>4.8615000000000004</v>
       </c>
       <c r="L18" s="1">
-        <v>4.2300000000000004</v>
+        <v>4.4415000000000004</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
       <c r="E19" s="1">
-        <v>5.91</v>
+        <v>6.2055000000000007</v>
       </c>
       <c r="F19" s="1">
-        <v>5.59</v>
+        <v>5.8695000000000004</v>
       </c>
       <c r="G19" s="1">
-        <v>5.28</v>
+        <v>5.8608000000000011</v>
       </c>
       <c r="H19" s="1">
-        <v>5.05</v>
+        <v>5.3025000000000002</v>
       </c>
       <c r="I19" s="1">
-        <v>4.95</v>
+        <v>5.1975000000000007</v>
       </c>
       <c r="J19" s="1">
-        <v>4.8899999999999997</v>
+        <v>5.1345000000000001</v>
       </c>
       <c r="K19" s="1">
-        <v>4.87</v>
+        <v>5.1135000000000002</v>
       </c>
       <c r="L19" s="1">
-        <v>4.8099999999999996</v>
+        <v>5.0504999999999995</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1">
-        <v>5.53</v>
+        <v>5.8065000000000007</v>
       </c>
       <c r="F20" s="1">
-        <v>5.51</v>
+        <v>5.7854999999999999</v>
       </c>
       <c r="G20" s="1">
-        <v>5.44</v>
+        <v>6.0384000000000011</v>
       </c>
       <c r="H20" s="1">
-        <v>5.24</v>
+        <v>5.5020000000000007</v>
       </c>
       <c r="I20" s="1">
-        <v>5.28</v>
+        <v>5.5440000000000005</v>
       </c>
       <c r="J20" s="1">
-        <v>4.9800000000000004</v>
+        <v>5.229000000000001</v>
       </c>
       <c r="K20" s="1">
-        <v>4.79</v>
+        <v>5.0295000000000005</v>
       </c>
       <c r="L20" s="1">
-        <v>4.71</v>
+        <v>4.9455</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" s="1">
-        <v>5.23</v>
+        <v>5.4915000000000003</v>
       </c>
       <c r="F21" s="1">
-        <v>5.23</v>
+        <v>5.4915000000000003</v>
       </c>
       <c r="G21" s="1">
-        <v>5.04</v>
+        <v>5.5944000000000003</v>
       </c>
       <c r="H21" s="1">
-        <v>5.15</v>
+        <v>5.4075000000000006</v>
       </c>
       <c r="I21" s="1">
-        <v>5.01</v>
+        <v>5.2605000000000004</v>
       </c>
       <c r="J21" s="1">
-        <v>4.83</v>
+        <v>5.0715000000000003</v>
       </c>
       <c r="K21" s="1">
-        <v>4.79</v>
+        <v>5.0295000000000005</v>
       </c>
       <c r="L21" s="1">
-        <v>4.68</v>
+        <v>4.9139999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +2083,7 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -1881,7 +2094,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -1916,10 +2129,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1">
-        <v>11.5</v>
+        <v>11.73</v>
       </c>
       <c r="F4" s="1">
         <v>11.46</v>
@@ -1928,7 +2141,7 @@
         <v>11.05</v>
       </c>
       <c r="H4" s="1">
-        <v>10.34</v>
+        <v>10.1332</v>
       </c>
       <c r="I4" s="1">
         <v>10.29</v>
@@ -1937,7 +2150,7 @@
         <v>10.11</v>
       </c>
       <c r="K4" s="1">
-        <v>9.81</v>
+        <v>9.7119</v>
       </c>
       <c r="L4" s="1">
         <v>9.56</v>
@@ -1951,10 +2164,10 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1">
-        <v>11.71</v>
+        <v>11.9442</v>
       </c>
       <c r="F5" s="1">
         <v>11.02</v>
@@ -1963,7 +2176,7 @@
         <v>10.95</v>
       </c>
       <c r="H5" s="1">
-        <v>10.75</v>
+        <v>10.535</v>
       </c>
       <c r="I5" s="1">
         <v>10.51</v>
@@ -1972,7 +2185,7 @@
         <v>10.27</v>
       </c>
       <c r="K5" s="1">
-        <v>9.91</v>
+        <v>9.8109000000000002</v>
       </c>
       <c r="L5" s="1">
         <v>9.76</v>
@@ -1986,10 +2199,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1">
-        <v>10.86</v>
+        <v>11.077199999999999</v>
       </c>
       <c r="F6" s="1">
         <v>10.51</v>
@@ -1998,7 +2211,7 @@
         <v>10.24</v>
       </c>
       <c r="H6" s="1">
-        <v>10.29</v>
+        <v>10.084199999999999</v>
       </c>
       <c r="I6" s="1">
         <v>10.050000000000001</v>
@@ -2007,7 +2220,7 @@
         <v>9.68</v>
       </c>
       <c r="K6" s="1">
-        <v>9.9499999999999993</v>
+        <v>9.8504999999999985</v>
       </c>
       <c r="L6" s="1">
         <v>9.0500000000000007</v>
@@ -2018,34 +2231,34 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
-        <v>11.51</v>
+        <v>12.0855</v>
       </c>
       <c r="F7" s="1">
-        <v>11.39</v>
+        <v>11.9595</v>
       </c>
       <c r="G7" s="1">
-        <v>11.15</v>
+        <v>11.707500000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>10.31</v>
+        <v>10.825500000000002</v>
       </c>
       <c r="I7" s="1">
-        <v>10.16</v>
+        <v>10.668000000000001</v>
       </c>
       <c r="J7" s="1">
-        <v>10.050000000000001</v>
+        <v>10.552500000000002</v>
       </c>
       <c r="K7" s="1">
-        <v>9.76</v>
+        <v>10.247999999999999</v>
       </c>
       <c r="L7" s="1">
-        <v>9.84</v>
+        <v>10.332000000000001</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -2053,34 +2266,34 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
-        <v>11.71</v>
+        <v>12.295500000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>11.34</v>
+        <v>11.907</v>
       </c>
       <c r="G8" s="1">
-        <v>10.86</v>
+        <v>11.403</v>
       </c>
       <c r="H8" s="1">
-        <v>10.98</v>
+        <v>11.529000000000002</v>
       </c>
       <c r="I8" s="1">
-        <v>10.83</v>
+        <v>11.371500000000001</v>
       </c>
       <c r="J8" s="1">
-        <v>10.51</v>
+        <v>11.035500000000001</v>
       </c>
       <c r="K8" s="1">
-        <v>10.06</v>
+        <v>10.563000000000001</v>
       </c>
       <c r="L8" s="1">
-        <v>10.15</v>
+        <v>10.657500000000001</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -2088,454 +2301,454 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
-        <v>10.85</v>
+        <v>11.3925</v>
       </c>
       <c r="F9" s="1">
-        <v>10.45</v>
+        <v>10.9725</v>
       </c>
       <c r="G9" s="1">
-        <v>10.36</v>
+        <v>10.878</v>
       </c>
       <c r="H9" s="1">
-        <v>9.9600000000000009</v>
+        <v>10.458000000000002</v>
       </c>
       <c r="I9" s="1">
-        <v>9.81</v>
+        <v>10.300500000000001</v>
       </c>
       <c r="J9" s="1">
-        <v>9.77</v>
+        <v>10.2585</v>
       </c>
       <c r="K9" s="1">
-        <v>9.81</v>
+        <v>10.300500000000001</v>
       </c>
       <c r="L9" s="1">
-        <v>9.69</v>
+        <v>10.1745</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
-        <v>11.6</v>
+        <v>12.18</v>
       </c>
       <c r="F10" s="1">
-        <v>10.95</v>
+        <v>11.4975</v>
       </c>
       <c r="G10" s="1">
-        <v>10.48</v>
+        <v>11.004000000000001</v>
       </c>
       <c r="H10" s="1">
         <v>10.18</v>
       </c>
       <c r="I10" s="1">
-        <v>9.48</v>
+        <v>9.9540000000000006</v>
       </c>
       <c r="J10" s="1">
-        <v>8.9600000000000009</v>
+        <v>9.4080000000000013</v>
       </c>
       <c r="K10" s="1">
-        <v>8.8000000000000007</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="L10" s="1">
-        <v>8.9</v>
+        <v>9.3450000000000006</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1">
-        <v>12.7</v>
+        <v>13.334999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>11.4</v>
+        <v>11.97</v>
       </c>
       <c r="G11" s="1">
-        <v>11.6</v>
+        <v>12.18</v>
       </c>
       <c r="H11" s="1">
         <v>10.95</v>
       </c>
       <c r="I11" s="1">
-        <v>10.46</v>
+        <v>10.983000000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>9.5500000000000007</v>
+        <v>10.027500000000002</v>
       </c>
       <c r="K11" s="1">
-        <v>9.32</v>
+        <v>9.7860000000000014</v>
       </c>
       <c r="L11" s="1">
-        <v>9.1199999999999992</v>
+        <v>9.5759999999999987</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1">
-        <v>11.3</v>
+        <v>11.865000000000002</v>
       </c>
       <c r="F12" s="1">
-        <v>10.85</v>
+        <v>11.3925</v>
       </c>
       <c r="G12" s="1">
-        <v>10.52</v>
+        <v>11.045999999999999</v>
       </c>
       <c r="H12" s="1">
         <v>9.86</v>
       </c>
       <c r="I12" s="1">
-        <v>9.58</v>
+        <v>10.059000000000001</v>
       </c>
       <c r="J12" s="1">
-        <v>8.7799999999999994</v>
+        <v>9.2189999999999994</v>
       </c>
       <c r="K12" s="1">
-        <v>8.65</v>
+        <v>9.0825000000000014</v>
       </c>
       <c r="L12" s="1">
-        <v>8.23</v>
+        <v>8.6415000000000006</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1">
-        <v>13.2</v>
+        <v>13.86</v>
       </c>
       <c r="F13" s="1">
-        <v>11.9</v>
+        <v>12.495000000000001</v>
       </c>
       <c r="G13" s="1">
-        <v>11.22</v>
+        <v>11.781000000000001</v>
       </c>
       <c r="H13" s="1">
         <v>10.32</v>
       </c>
       <c r="I13" s="1">
-        <v>10.72</v>
+        <v>11.256000000000002</v>
       </c>
       <c r="J13" s="1">
-        <v>9.7100000000000009</v>
+        <v>10.195500000000001</v>
       </c>
       <c r="K13" s="1">
-        <v>9.23</v>
+        <v>9.9435000000000002</v>
       </c>
       <c r="L13" s="1">
-        <v>9.1300000000000008</v>
+        <v>10.111500000000001</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1">
-        <v>14.9</v>
+        <v>15.645000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>13.4</v>
+        <v>14.07</v>
       </c>
       <c r="G14" s="1">
-        <v>11.97</v>
+        <v>12.568500000000002</v>
       </c>
       <c r="H14" s="1">
         <v>11.1</v>
       </c>
       <c r="I14" s="1">
-        <v>10.95</v>
+        <v>11.4975</v>
       </c>
       <c r="J14" s="1">
-        <v>10.36</v>
+        <v>10.878</v>
       </c>
       <c r="K14" s="1">
-        <v>10.72</v>
+        <v>11.256000000000002</v>
       </c>
       <c r="L14" s="1">
-        <v>9.0500000000000007</v>
+        <v>9.5025000000000013</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1">
-        <v>13.5</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>12.12</v>
+        <v>12.725999999999999</v>
       </c>
       <c r="G15" s="1">
-        <v>11.68</v>
+        <v>12.263999999999999</v>
       </c>
       <c r="H15" s="1">
         <v>10.15</v>
       </c>
       <c r="I15" s="1">
-        <v>10.65</v>
+        <v>11.182500000000001</v>
       </c>
       <c r="J15" s="1">
-        <v>9.56</v>
+        <v>10.038</v>
       </c>
       <c r="K15" s="1">
-        <v>9.24</v>
+        <v>9.702</v>
       </c>
       <c r="L15" s="1">
-        <v>9.36</v>
+        <v>9.8279999999999994</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1">
-        <v>5.22</v>
+        <v>5.4809999999999999</v>
       </c>
       <c r="F16" s="1">
-        <v>5.31</v>
+        <v>5.5754999999999999</v>
       </c>
       <c r="G16" s="1">
-        <v>5.0199999999999996</v>
+        <v>5.4215999999999998</v>
       </c>
       <c r="H16" s="1">
         <v>4.84</v>
       </c>
       <c r="I16" s="1">
-        <v>4.63</v>
+        <v>4.8615000000000004</v>
       </c>
       <c r="J16" s="1">
-        <v>4.43</v>
+        <v>4.6514999999999995</v>
       </c>
       <c r="K16" s="1">
-        <v>4.33</v>
+        <v>4.5465</v>
       </c>
       <c r="L16" s="1">
-        <v>4.2300000000000004</v>
+        <v>4.4415000000000004</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1">
-        <v>5.26</v>
+        <v>5.5229999999999997</v>
       </c>
       <c r="F17" s="1">
-        <v>5.0599999999999996</v>
+        <v>5.3129999999999997</v>
       </c>
       <c r="G17" s="1">
-        <v>4.93</v>
+        <v>5.3243999999999998</v>
       </c>
       <c r="H17" s="1">
         <v>5</v>
       </c>
       <c r="I17" s="1">
-        <v>4.7300000000000004</v>
+        <v>4.9665000000000008</v>
       </c>
       <c r="J17" s="1">
-        <v>4.42</v>
+        <v>4.641</v>
       </c>
       <c r="K17" s="1">
-        <v>4.21</v>
+        <v>4.4205000000000005</v>
       </c>
       <c r="L17" s="1">
-        <v>4.28</v>
+        <v>4.4940000000000007</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1">
-        <v>5.09</v>
+        <v>5.3445</v>
       </c>
       <c r="F18" s="1">
-        <v>5.0599999999999996</v>
+        <v>5.3129999999999997</v>
       </c>
       <c r="G18" s="1">
-        <v>4.8600000000000003</v>
+        <v>5.248800000000001</v>
       </c>
       <c r="H18" s="1">
         <v>4.8600000000000003</v>
       </c>
       <c r="I18" s="1">
-        <v>4.71</v>
+        <v>4.9455</v>
       </c>
       <c r="J18" s="1">
-        <v>4.29</v>
+        <v>4.5045000000000002</v>
       </c>
       <c r="K18" s="1">
-        <v>4.13</v>
+        <v>4.3365</v>
       </c>
       <c r="L18" s="1">
-        <v>4.12</v>
+        <v>4.3260000000000005</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
       <c r="E19" s="1">
-        <v>5.59</v>
+        <v>5.8695000000000004</v>
       </c>
       <c r="F19" s="1">
-        <v>5.08</v>
+        <v>5.3340000000000005</v>
       </c>
       <c r="G19" s="1">
-        <v>4.97</v>
+        <v>5.5167000000000002</v>
       </c>
       <c r="H19" s="1">
-        <v>4.92</v>
+        <v>5.1660000000000004</v>
       </c>
       <c r="I19" s="1">
-        <v>4.6900000000000004</v>
+        <v>4.924500000000001</v>
       </c>
       <c r="J19" s="1">
-        <v>4.7300000000000004</v>
+        <v>4.9665000000000008</v>
       </c>
       <c r="K19" s="1">
-        <v>4.6500000000000004</v>
+        <v>4.8825000000000003</v>
       </c>
       <c r="L19" s="1">
-        <v>4.7</v>
+        <v>4.9350000000000005</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1">
-        <v>5.33</v>
+        <v>5.5965000000000007</v>
       </c>
       <c r="F20" s="1">
-        <v>5.33</v>
+        <v>5.5965000000000007</v>
       </c>
       <c r="G20" s="1">
-        <v>4.7699999999999996</v>
+        <v>5.2946999999999997</v>
       </c>
       <c r="H20" s="1">
-        <v>4.79</v>
+        <v>5.0295000000000005</v>
       </c>
       <c r="I20" s="1">
-        <v>4.6500000000000004</v>
+        <v>4.8825000000000003</v>
       </c>
       <c r="J20" s="1">
-        <v>4.71</v>
+        <v>4.9455</v>
       </c>
       <c r="K20" s="1">
-        <v>4.54</v>
+        <v>4.7670000000000003</v>
       </c>
       <c r="L20" s="1">
-        <v>4.67</v>
+        <v>4.9035000000000002</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" s="1">
-        <v>5.09</v>
+        <v>5.3445</v>
       </c>
       <c r="F21" s="1">
-        <v>4.99</v>
+        <v>5.2395000000000005</v>
       </c>
       <c r="G21" s="1">
-        <v>4.88</v>
+        <v>5.4168000000000003</v>
       </c>
       <c r="H21" s="1">
-        <v>4.59</v>
+        <v>4.8194999999999997</v>
       </c>
       <c r="I21" s="1">
-        <v>4.62</v>
+        <v>4.851</v>
       </c>
       <c r="J21" s="1">
-        <v>4.63</v>
+        <v>4.8615000000000004</v>
       </c>
       <c r="K21" s="1">
-        <v>4.5</v>
+        <v>4.7250000000000005</v>
       </c>
       <c r="L21" s="1">
-        <v>4.43</v>
+        <v>4.6514999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -2544,26 +2757,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="95ec026b-a4ad-461a-a1d4-c6b927e959dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="951160fc-ff5a-45f7-b050-f4bae28803d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100100A38896A05B94AA42235B986E30978" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4bf31abf3bdff13eb8ffced64c31c2c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="95ec026b-a4ad-461a-a1d4-c6b927e959dc" xmlns:ns3="951160fc-ff5a-45f7-b050-f4bae28803d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5b6ee4a3c3b8aac6ba9922f122fd761" ns2:_="" ns3:_="">
     <xsd:import namespace="95ec026b-a4ad-461a-a1d4-c6b927e959dc"/>
@@ -2770,10 +2963,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="95ec026b-a4ad-461a-a1d4-c6b927e959dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="951160fc-ff5a-45f7-b050-f4bae28803d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD7541A-4617-41A2-8628-D1F9E91F5839}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED17B6C-AB57-46A8-BFAB-081AE907A653}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="95ec026b-a4ad-461a-a1d4-c6b927e959dc"/>
+    <ds:schemaRef ds:uri="951160fc-ff5a-45f7-b050-f4bae28803d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2790,20 +3014,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED17B6C-AB57-46A8-BFAB-081AE907A653}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD7541A-4617-41A2-8628-D1F9E91F5839}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="95ec026b-a4ad-461a-a1d4-c6b927e959dc"/>
-    <ds:schemaRef ds:uri="951160fc-ff5a-45f7-b050-f4bae28803d7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Homepage references.xlsx
+++ b/Homepage references.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4baf5f27aaa308f5/Desktop/Measurements Github Repo/measurements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{2C9B8835-76DE-4971-9A34-FBC49FD6DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5587FD16-0F35-4FC6-B18D-60EE88006A00}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{2C9B8835-76DE-4971-9A34-FBC49FD6DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B729CD4-A8F6-42D0-B053-D279B8E76604}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A392E83A-501C-4FB4-93CE-0DA18CB18A6B}"/>
+    <workbookView xWindow="7215" yWindow="3930" windowWidth="7500" windowHeight="9810" xr2:uid="{A392E83A-501C-4FB4-93CE-0DA18CB18A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -505,7 +505,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -869,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="E13" s="1">
-        <v>13.844999999999999</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1">
         <v>12.446000000000002</v>
@@ -881,16 +881,16 @@
         <v>11.154999999999998</v>
       </c>
       <c r="I13" s="1">
-        <v>11.577599999999999</v>
+        <v>10.853999999999999</v>
       </c>
       <c r="J13" s="1">
-        <v>10.880999999999998</v>
+        <v>10.276499999999999</v>
       </c>
       <c r="K13" s="1">
-        <v>10.98</v>
+        <v>10.37</v>
       </c>
       <c r="L13" s="1">
-        <v>10.521000000000001</v>
+        <v>9.9365000000000006</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
@@ -904,28 +904,28 @@
         <v>24</v>
       </c>
       <c r="E14" s="1">
-        <v>12.156000632838809</v>
+        <v>10.570435332903314</v>
       </c>
       <c r="F14" s="1">
-        <v>11.030749344776938</v>
+        <v>10.35751112185628</v>
       </c>
       <c r="G14" s="1">
-        <v>10.70361851495923</v>
+        <v>10.050346023435896</v>
       </c>
       <c r="H14" s="1">
-        <v>10.081766169748226</v>
+        <v>9.8017171094774422</v>
       </c>
       <c r="I14" s="1">
-        <v>10.248544047521285</v>
+        <v>9.4893926365937826</v>
       </c>
       <c r="J14" s="1">
-        <v>9.6455123974865149</v>
+        <v>9.1378538502503837</v>
       </c>
       <c r="K14" s="1">
-        <v>9.3518868866449232</v>
+        <v>9.1485849978048162</v>
       </c>
       <c r="L14" s="1">
-        <v>9.1785042314062117</v>
+        <v>8.7195790198359013</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
@@ -945,13 +945,13 @@
         <v>8.6741353772454346</v>
       </c>
       <c r="G15" s="1">
-        <v>8.0932399573808258</v>
+        <v>8.4451199555278187</v>
       </c>
       <c r="H15" s="1">
-        <v>7.7533737771005748</v>
+        <v>8.0764310178130998</v>
       </c>
       <c r="I15" s="1">
-        <v>7.4603356797274323</v>
+        <v>7.7711829997160748</v>
       </c>
       <c r="J15" s="1">
         <v>7.8347794911925126</v>
@@ -2964,6 +2964,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="95ec026b-a4ad-461a-a1d4-c6b927e959dc">
@@ -2972,15 +2981,6 @@
     <TaxCatchAll xmlns="951160fc-ff5a-45f7-b050-f4bae28803d7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3003,6 +3003,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD7541A-4617-41A2-8628-D1F9E91F5839}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E65F761-03A7-41D7-A089-3F63BCC3640B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3011,12 +3019,4 @@
     <ds:schemaRef ds:uri="951160fc-ff5a-45f7-b050-f4bae28803d7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD7541A-4617-41A2-8628-D1F9E91F5839}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>